--- a/artfynd/A 39285-2026 artfynd.xlsx
+++ b/artfynd/A 39285-2026 artfynd.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Johanna Björkman</t>
+          <t>Johanna Björkman, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 39285-2026 artfynd.xlsx
+++ b/artfynd/A 39285-2026 artfynd.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johanna Björkman, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Johanna Björkman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 39285-2026 artfynd.xlsx
+++ b/artfynd/A 39285-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136544433</v>
       </c>
       <c r="B2" t="n">
-        <v>43282</v>
+        <v>43295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136550517</v>
       </c>
       <c r="B3" t="n">
-        <v>43282</v>
+        <v>43295</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39285-2026 artfynd.xlsx
+++ b/artfynd/A 39285-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136544433</v>
       </c>
       <c r="B2" t="n">
-        <v>43295</v>
+        <v>43297</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136550517</v>
       </c>
       <c r="B3" t="n">
-        <v>43295</v>
+        <v>43297</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
